--- a/Microcontroladores/Semana 7/Lista sensores asignados.xlsx
+++ b/Microcontroladores/Semana 7/Lista sensores asignados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pregrado Ingenieria en Sistemas\Semestre 6\Microcontroladores\Semana 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325194F8-72CA-43D3-9777-F22301AAE1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B9A913-0438-4ED6-8D05-271D19EBEE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7C36F5B-BE09-49C1-B69D-04D9C3CFDC18}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E7C36F5B-BE09-49C1-B69D-04D9C3CFDC18}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -402,6 +402,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,27 +431,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,161 +767,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3014608-9576-4A3A-8229-5A6DF4996148}">
   <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="21.86328125" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="12"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="12"/>
-    </row>
-    <row r="4" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="13"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="12"/>
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="12"/>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13"/>
+      <c r="B4" s="10"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="11"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="11"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="11"/>
-    </row>
-    <row r="9" spans="1:2" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="12"/>
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="12"/>
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="13"/>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="11"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="11"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="11"/>
-    </row>
-    <row r="13" spans="1:2" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="11"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="12"/>
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8"/>
+    </row>
+    <row r="13" spans="1:2" ht="29.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" s="3"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="12"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="12"/>
-    </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="13"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" s="12"/>
+      <c r="B16" s="9"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="12"/>
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="13"/>
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="3"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="8"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="8"/>
-    </row>
-    <row r="24" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="8"/>
-    </row>
-    <row r="25" spans="1:2" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="9"/>
-    </row>
-    <row r="26" spans="1:2" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="12"/>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="12"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="12"/>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="12"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:2" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="13"/>
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:2" ht="21.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="8"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="8"/>
-    </row>
-    <row r="31" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="9"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="12"/>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="12"/>
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" s="12"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="13"/>
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
         <v>6</v>
       </c>
@@ -929,7 +929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>7</v>
       </c>
@@ -937,7 +937,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
         <v>8</v>
       </c>
@@ -945,7 +945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
         <v>9</v>
       </c>
@@ -955,18 +955,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="B9:B13"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="B15:B18"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
